--- a/data/stx_xlsx/SOBIV.ST.xlsx
+++ b/data/stx_xlsx/SOBIV.ST.xlsx
@@ -18643,9 +18643,7 @@
       <c r="P127" s="15">
         <v>0.0</v>
       </c>
-      <c r="Q127" s="16">
-        <v>142.54</v>
-      </c>
+      <c r="Q127" s="16"/>
       <c r="R127" s="15"/>
       <c r="S127" s="15"/>
       <c r="T127" s="15"/>
